--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/153.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/153.xlsx
@@ -426,13 +426,13 @@
         <v>-0.9612650565138582</v>
       </c>
       <c r="E2">
-        <v>-17.8400612841452</v>
+        <v>-14.80507347573052</v>
       </c>
       <c r="F2">
-        <v>3.646828529491717</v>
+        <v>3.658758676826836</v>
       </c>
       <c r="G2">
-        <v>-10.76224040210288</v>
+        <v>-8.719643736009175</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.8038382299907755</v>
       </c>
       <c r="E3">
-        <v>-16.41795289219843</v>
+        <v>-14.60796711607266</v>
       </c>
       <c r="F3">
-        <v>3.182053117333387</v>
+        <v>3.924184160031853</v>
       </c>
       <c r="G3">
-        <v>-10.18050471885107</v>
+        <v>-7.239670973769068</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.6420465910522365</v>
       </c>
       <c r="E4">
-        <v>-17.67023898038356</v>
+        <v>-15.60154148419959</v>
       </c>
       <c r="F4">
-        <v>3.759055745222994</v>
+        <v>3.575519349989124</v>
       </c>
       <c r="G4">
-        <v>-10.72549996770805</v>
+        <v>-8.169487346656471</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.4812057831254855</v>
       </c>
       <c r="E5">
-        <v>-18.3951389856354</v>
+        <v>-16.55139796425646</v>
       </c>
       <c r="F5">
-        <v>3.713787123394807</v>
+        <v>4.048883275379679</v>
       </c>
       <c r="G5">
-        <v>-10.10893072429202</v>
+        <v>-7.735954855561213</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.318761869168959</v>
       </c>
       <c r="E6">
-        <v>-17.66687432419586</v>
+        <v>-16.4954531963657</v>
       </c>
       <c r="F6">
-        <v>3.636987524746459</v>
+        <v>3.706169456758662</v>
       </c>
       <c r="G6">
-        <v>-10.58317961497478</v>
+        <v>-7.449182158767385</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.155523058803372</v>
       </c>
       <c r="E7">
-        <v>-19.58181201392339</v>
+        <v>-16.38600903654832</v>
       </c>
       <c r="F7">
-        <v>3.873675286013556</v>
+        <v>4.625866022451619</v>
       </c>
       <c r="G7">
-        <v>-10.6477882217192</v>
+        <v>-6.873984802955634</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.008947251040180786</v>
       </c>
       <c r="E8">
-        <v>-20.56596715611436</v>
+        <v>-17.53437570320543</v>
       </c>
       <c r="F8">
-        <v>4.148733025378326</v>
+        <v>4.323048034684231</v>
       </c>
       <c r="G8">
-        <v>-9.04180616461781</v>
+        <v>-7.220757827103212</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.1723242574054615</v>
       </c>
       <c r="E9">
-        <v>-19.48514267928165</v>
+        <v>-18.2182024492077</v>
       </c>
       <c r="F9">
-        <v>4.17497736143382</v>
+        <v>4.594036833366451</v>
       </c>
       <c r="G9">
-        <v>-8.492368163647129</v>
+        <v>-6.136219797892432</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.3360941397415704</v>
       </c>
       <c r="E10">
-        <v>-20.00329973218731</v>
+        <v>-20.11748067581671</v>
       </c>
       <c r="F10">
-        <v>4.784707128673229</v>
+        <v>4.390145794310992</v>
       </c>
       <c r="G10">
-        <v>-8.880575975764225</v>
+        <v>-6.421118725911032</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.5015285753540643</v>
       </c>
       <c r="E11">
-        <v>-20.8209157142722</v>
+        <v>-19.08352137648939</v>
       </c>
       <c r="F11">
-        <v>5.036378399522165</v>
+        <v>4.782846615486542</v>
       </c>
       <c r="G11">
-        <v>-7.830113391789164</v>
+        <v>-6.814169866152082</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.6709776920029142</v>
       </c>
       <c r="E12">
-        <v>-21.86536295940128</v>
+        <v>-19.99175665194176</v>
       </c>
       <c r="F12">
-        <v>5.063600209112962</v>
+        <v>5.099708744200992</v>
       </c>
       <c r="G12">
-        <v>-7.826302953873462</v>
+        <v>-6.040538410716416</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.8475617856926773</v>
       </c>
       <c r="E13">
-        <v>-22.11631287501035</v>
+        <v>-20.92650161423504</v>
       </c>
       <c r="F13">
-        <v>5.417402553787853</v>
+        <v>5.320311267240529</v>
       </c>
       <c r="G13">
-        <v>-7.389320874326283</v>
+        <v>-5.648460570863912</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.032068710567395</v>
       </c>
       <c r="E14">
-        <v>-23.15095597391283</v>
+        <v>-21.26603300990814</v>
       </c>
       <c r="F14">
-        <v>5.512346712027121</v>
+        <v>5.282627177352373</v>
       </c>
       <c r="G14">
-        <v>-7.755003734594179</v>
+        <v>-4.490054339035374</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.228193974597716</v>
       </c>
       <c r="E15">
-        <v>-24.26231142250525</v>
+        <v>-23.59249124660871</v>
       </c>
       <c r="F15">
-        <v>5.477212337004783</v>
+        <v>6.041300717084746</v>
       </c>
       <c r="G15">
-        <v>-6.740877698458157</v>
+        <v>-4.571732118580273</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.440571534351661</v>
       </c>
       <c r="E16">
-        <v>-24.08784290441174</v>
+        <v>-22.47073842169468</v>
       </c>
       <c r="F16">
-        <v>5.519644628845785</v>
+        <v>5.914913388970014</v>
       </c>
       <c r="G16">
-        <v>-7.410375943956048</v>
+        <v>-3.059008129320157</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.674226367891903</v>
       </c>
       <c r="E17">
-        <v>-25.9784762741401</v>
+        <v>-23.55194329034403</v>
       </c>
       <c r="F17">
-        <v>6.264525851321545</v>
+        <v>6.334135220913593</v>
       </c>
       <c r="G17">
-        <v>-6.255776839497671</v>
+        <v>-3.379591427706561</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.933583933069289</v>
       </c>
       <c r="E18">
-        <v>-25.49474015216675</v>
+        <v>-25.68066570949967</v>
       </c>
       <c r="F18">
-        <v>6.116668896861055</v>
+        <v>6.78167065068486</v>
       </c>
       <c r="G18">
-        <v>-6.419162193497323</v>
+        <v>-3.479818193907996</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.219946426831575</v>
       </c>
       <c r="E19">
-        <v>-26.75569826807657</v>
+        <v>-25.7338164089277</v>
       </c>
       <c r="F19">
-        <v>6.452407861950501</v>
+        <v>6.628079737062192</v>
       </c>
       <c r="G19">
-        <v>-5.3345447111936</v>
+        <v>-3.087568205687449</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.531589902804321</v>
       </c>
       <c r="E20">
-        <v>-27.00749500832506</v>
+        <v>-25.29875685406279</v>
       </c>
       <c r="F20">
-        <v>6.644083795284279</v>
+        <v>6.864500764025588</v>
       </c>
       <c r="G20">
-        <v>-4.938348552690242</v>
+        <v>-3.314055868211149</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.865973539259729</v>
       </c>
       <c r="E21">
-        <v>-26.712858903964</v>
+        <v>-25.00825524647074</v>
       </c>
       <c r="F21">
-        <v>6.806945796879078</v>
+        <v>7.124351334609765</v>
       </c>
       <c r="G21">
-        <v>-4.488647357181184</v>
+        <v>-2.840518744819337</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.215589773949802</v>
       </c>
       <c r="E22">
-        <v>-27.53870312332083</v>
+        <v>-27.66944469639628</v>
       </c>
       <c r="F22">
-        <v>6.963276949870206</v>
+        <v>7.179189256675092</v>
       </c>
       <c r="G22">
-        <v>-5.007307216273261</v>
+        <v>-2.392595312264867</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.569632434779655</v>
       </c>
       <c r="E23">
-        <v>-28.47235672337825</v>
+        <v>-26.70098071664189</v>
       </c>
       <c r="F23">
-        <v>7.316776112075673</v>
+        <v>7.492242552071469</v>
       </c>
       <c r="G23">
-        <v>-4.253572139528615</v>
+        <v>-1.981975106846904</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.915009923242331</v>
       </c>
       <c r="E24">
-        <v>-29.27368831293155</v>
+        <v>-28.51071742669723</v>
       </c>
       <c r="F24">
-        <v>7.495007642462014</v>
+        <v>7.441669065395755</v>
       </c>
       <c r="G24">
-        <v>-3.373082895176354</v>
+        <v>-2.401586753949528</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.236078437303023</v>
       </c>
       <c r="E25">
-        <v>-29.73074719452572</v>
+        <v>-28.89366783115587</v>
       </c>
       <c r="F25">
-        <v>7.278520448679586</v>
+        <v>7.502252543766899</v>
       </c>
       <c r="G25">
-        <v>-3.697460078750762</v>
+        <v>-1.416100247273741</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.523214565661367</v>
       </c>
       <c r="E26">
-        <v>-29.11532757688332</v>
+        <v>-28.52485532254918</v>
       </c>
       <c r="F26">
-        <v>7.029102337166266</v>
+        <v>7.380691284140878</v>
       </c>
       <c r="G26">
-        <v>-3.729896803944542</v>
+        <v>-1.647050525184378</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.767776474907047</v>
       </c>
       <c r="E27">
-        <v>-30.23551807826471</v>
+        <v>-27.49245381828049</v>
       </c>
       <c r="F27">
-        <v>6.960394231308464</v>
+        <v>7.783738414177393</v>
       </c>
       <c r="G27">
-        <v>-2.63228211985364</v>
+        <v>-1.655151430118974</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.965195007688886</v>
       </c>
       <c r="E28">
-        <v>-29.8325744610622</v>
+        <v>-29.575049201194</v>
       </c>
       <c r="F28">
-        <v>7.778352369324391</v>
+        <v>7.417407840902563</v>
       </c>
       <c r="G28">
-        <v>-4.109421055112129</v>
+        <v>-1.688683945886252</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.11449558721455</v>
       </c>
       <c r="E29">
-        <v>-30.81170752557866</v>
+        <v>-28.95864237621793</v>
       </c>
       <c r="F29">
-        <v>7.00643157808645</v>
+        <v>7.624789620193419</v>
       </c>
       <c r="G29">
-        <v>-3.205973177445023</v>
+        <v>-2.220668750773896</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.217986741357571</v>
       </c>
       <c r="E30">
-        <v>-29.75037586511197</v>
+        <v>-28.38431413172113</v>
       </c>
       <c r="F30">
-        <v>7.103491386672467</v>
+        <v>7.746420462681276</v>
       </c>
       <c r="G30">
-        <v>-4.759360597564006</v>
+        <v>-1.259829255637984</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.283596199917344</v>
       </c>
       <c r="E31">
-        <v>-30.1773588865842</v>
+        <v>-28.62397456162907</v>
       </c>
       <c r="F31">
-        <v>7.557342289522677</v>
+        <v>7.221063228886607</v>
       </c>
       <c r="G31">
-        <v>-3.900002565388913</v>
+        <v>-1.610061799874101</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.320847772884036</v>
       </c>
       <c r="E32">
-        <v>-29.54077770990395</v>
+        <v>-28.07196716551607</v>
       </c>
       <c r="F32">
-        <v>7.193160501290708</v>
+        <v>7.373819148167253</v>
       </c>
       <c r="G32">
-        <v>-4.311503375920322</v>
+        <v>-2.125596503977107</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.339033821086862</v>
       </c>
       <c r="E33">
-        <v>-29.99374058675818</v>
+        <v>-28.71380137204521</v>
       </c>
       <c r="F33">
-        <v>7.07350282995632</v>
+        <v>7.332188715972161</v>
       </c>
       <c r="G33">
-        <v>-4.329502812017339</v>
+        <v>-1.86084886665605</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.344905630106799</v>
       </c>
       <c r="E34">
-        <v>-29.92351754032124</v>
+        <v>-26.6619679130658</v>
       </c>
       <c r="F34">
-        <v>7.162428070646847</v>
+        <v>7.713665158839778</v>
       </c>
       <c r="G34">
-        <v>-3.83601303066034</v>
+        <v>-1.137372176140343</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.344247810762522</v>
       </c>
       <c r="E35">
-        <v>-29.27752393041605</v>
+        <v>-26.36859072447888</v>
       </c>
       <c r="F35">
-        <v>6.827615220313731</v>
+        <v>7.042409231124838</v>
       </c>
       <c r="G35">
-        <v>-3.846252548013306</v>
+        <v>-1.866784674807964</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.339623546969562</v>
       </c>
       <c r="E36">
-        <v>-28.79820307060017</v>
+        <v>-28.37588211311884</v>
       </c>
       <c r="F36">
-        <v>6.844997681894077</v>
+        <v>7.550784933162117</v>
       </c>
       <c r="G36">
-        <v>-4.720084285286092</v>
+        <v>-1.833119737219115</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.331938521460843</v>
       </c>
       <c r="E37">
-        <v>-29.15564910944762</v>
+        <v>-26.46429549415699</v>
       </c>
       <c r="F37">
-        <v>7.105549051301021</v>
+        <v>7.059644243307484</v>
       </c>
       <c r="G37">
-        <v>-4.509765327176194</v>
+        <v>-1.920521450001413</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.318302031859011</v>
       </c>
       <c r="E38">
-        <v>-27.64671628535178</v>
+        <v>-27.33898383416054</v>
       </c>
       <c r="F38">
-        <v>6.920735313532035</v>
+        <v>7.133635676460342</v>
       </c>
       <c r="G38">
-        <v>-4.997153773104317</v>
+        <v>-2.666910426194417</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.293030650956792</v>
       </c>
       <c r="E39">
-        <v>-26.57398872004478</v>
+        <v>-25.49387974210529</v>
       </c>
       <c r="F39">
-        <v>6.913583189376264</v>
+        <v>7.331077046917604</v>
       </c>
       <c r="G39">
-        <v>-4.712188634174931</v>
+        <v>-2.455833353156025</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.250982536921519</v>
       </c>
       <c r="E40">
-        <v>-28.42789163709694</v>
+        <v>-25.46626963608053</v>
       </c>
       <c r="F40">
-        <v>6.811760268224149</v>
+        <v>6.906482423999467</v>
       </c>
       <c r="G40">
-        <v>-5.610693867351906</v>
+        <v>-1.934429051811892</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.187696004814356</v>
       </c>
       <c r="E41">
-        <v>-26.13670568444211</v>
+        <v>-26.21375766968263</v>
       </c>
       <c r="F41">
-        <v>6.856384420212958</v>
+        <v>6.899691468031317</v>
       </c>
       <c r="G41">
-        <v>-4.840356404727815</v>
+        <v>-2.419758338414587</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.101168233542485</v>
       </c>
       <c r="E42">
-        <v>-26.39563024277868</v>
+        <v>-24.08783837593773</v>
       </c>
       <c r="F42">
-        <v>6.760615208040502</v>
+        <v>7.213013154466202</v>
       </c>
       <c r="G42">
-        <v>-4.977128283137265</v>
+        <v>-3.314267743125662</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.989818695733881</v>
       </c>
       <c r="E43">
-        <v>-25.08958211117449</v>
+        <v>-23.96161621992193</v>
       </c>
       <c r="F43">
-        <v>7.218061225418862</v>
+        <v>6.979751520777083</v>
       </c>
       <c r="G43">
-        <v>-5.642322819434103</v>
+        <v>-1.451423768177765</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.854030779176023</v>
       </c>
       <c r="E44">
-        <v>-25.20573294099723</v>
+        <v>-23.69017495942816</v>
       </c>
       <c r="F44">
-        <v>7.467451172440486</v>
+        <v>7.669369040342477</v>
       </c>
       <c r="G44">
-        <v>-5.358486576533609</v>
+        <v>-2.204774821639855</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.694871659430356</v>
       </c>
       <c r="E45">
-        <v>-25.32633978924351</v>
+        <v>-24.58948914108543</v>
       </c>
       <c r="F45">
-        <v>7.559128249643114</v>
+        <v>7.520292729065067</v>
       </c>
       <c r="G45">
-        <v>-5.434407317385715</v>
+        <v>-2.618016979124921</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.517908142757837</v>
       </c>
       <c r="E46">
-        <v>-25.35369630072385</v>
+        <v>-22.01740647420882</v>
       </c>
       <c r="F46">
-        <v>7.332720527844758</v>
+        <v>7.317110772506404</v>
       </c>
       <c r="G46">
-        <v>-5.52323587529544</v>
+        <v>-2.388834532532255</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.328110221735986</v>
       </c>
       <c r="E47">
-        <v>-26.15165870561544</v>
+        <v>-23.07146314118219</v>
       </c>
       <c r="F47">
-        <v>7.19951076580057</v>
+        <v>7.12375822354936</v>
       </c>
       <c r="G47">
-        <v>-5.462262247553143</v>
+        <v>-3.083906742321016</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.12965146766972</v>
       </c>
       <c r="E48">
-        <v>-24.39356018466956</v>
+        <v>-22.31528949443338</v>
       </c>
       <c r="F48">
-        <v>6.454997338451652</v>
+        <v>7.31542587320911</v>
       </c>
       <c r="G48">
-        <v>-5.854009032851721</v>
+        <v>-3.11027523754131</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.925343293902315</v>
       </c>
       <c r="E49">
-        <v>-23.74805791419421</v>
+        <v>-20.96977571185234</v>
       </c>
       <c r="F49">
-        <v>7.246861903279394</v>
+        <v>7.387311596424051</v>
       </c>
       <c r="G49">
-        <v>-6.009253755370303</v>
+        <v>-2.478709222832389</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.715047067662295</v>
       </c>
       <c r="E50">
-        <v>-24.69919595239525</v>
+        <v>-21.20382989093878</v>
       </c>
       <c r="F50">
-        <v>6.989070654058578</v>
+        <v>7.456791740701262</v>
       </c>
       <c r="G50">
-        <v>-6.164359434976237</v>
+        <v>-3.278907806220706</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.501388426256391</v>
       </c>
       <c r="E51">
-        <v>-23.78795377020178</v>
+        <v>-20.18024985403703</v>
       </c>
       <c r="F51">
-        <v>6.97418157836066</v>
+        <v>7.289287568181174</v>
       </c>
       <c r="G51">
-        <v>-6.80114618000059</v>
+        <v>-2.559503086718302</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.284523504781566</v>
       </c>
       <c r="E52">
-        <v>-22.4389304202648</v>
+        <v>-18.77226577252018</v>
       </c>
       <c r="F52">
-        <v>7.247605777207109</v>
+        <v>7.095489357561425</v>
       </c>
       <c r="G52">
-        <v>-6.091679718207078</v>
+        <v>-3.666043001583079</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.063624749377045</v>
       </c>
       <c r="E53">
-        <v>-20.89573516182692</v>
+        <v>-20.36892872356661</v>
       </c>
       <c r="F53">
-        <v>6.714832998422579</v>
+        <v>7.516296684713962</v>
       </c>
       <c r="G53">
-        <v>-5.769924486699772</v>
+        <v>-2.867281194958805</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.837225649348861</v>
       </c>
       <c r="E54">
-        <v>-21.30558923036514</v>
+        <v>-20.01460733178446</v>
       </c>
       <c r="F54">
-        <v>7.069467023969881</v>
+        <v>7.291714684671377</v>
       </c>
       <c r="G54">
-        <v>-7.367272641034737</v>
+        <v>-4.908166309008707</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.603445591565275</v>
       </c>
       <c r="E55">
-        <v>-21.80810946252231</v>
+        <v>-18.36025162188031</v>
       </c>
       <c r="F55">
-        <v>7.215786528530774</v>
+        <v>7.892065676176291</v>
       </c>
       <c r="G55">
-        <v>-7.646854832917268</v>
+        <v>-4.174705013146557</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.362804005566812</v>
       </c>
       <c r="E56">
-        <v>-22.27418906433976</v>
+        <v>-18.59458656635523</v>
       </c>
       <c r="F56">
-        <v>6.627518103963094</v>
+        <v>7.120805922125783</v>
       </c>
       <c r="G56">
-        <v>-7.194617759525127</v>
+        <v>-4.64019751087794</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.117070591167963</v>
       </c>
       <c r="E57">
-        <v>-21.07706884651607</v>
+        <v>-18.10556118674091</v>
       </c>
       <c r="F57">
-        <v>6.348777443125477</v>
+        <v>7.426147117002097</v>
       </c>
       <c r="G57">
-        <v>-7.257763105141185</v>
+        <v>-4.302895957518216</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.867568718976375</v>
       </c>
       <c r="E58">
-        <v>-19.60037875735484</v>
+        <v>-16.42093262809547</v>
       </c>
       <c r="F58">
-        <v>6.274850622630038</v>
+        <v>7.262673780264032</v>
       </c>
       <c r="G58">
-        <v>-7.063205654343757</v>
+        <v>-4.833675723829566</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.61623102557534</v>
       </c>
       <c r="E59">
-        <v>-21.68313716533263</v>
+        <v>-18.50641264895188</v>
       </c>
       <c r="F59">
-        <v>6.482573689290848</v>
+        <v>7.134909705525847</v>
       </c>
       <c r="G59">
-        <v>-6.962674317952709</v>
+        <v>-5.250370780312091</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.365589412917773</v>
       </c>
       <c r="E60">
-        <v>-20.37911326160987</v>
+        <v>-16.76270108992837</v>
       </c>
       <c r="F60">
-        <v>6.522406564221865</v>
+        <v>6.969045700463302</v>
       </c>
       <c r="G60">
-        <v>-7.321769192597455</v>
+        <v>-5.129439862308054</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.118522698299423</v>
       </c>
       <c r="E61">
-        <v>-20.11542474861723</v>
+        <v>-15.62612204111322</v>
       </c>
       <c r="F61">
-        <v>6.419032939291709</v>
+        <v>7.057329784784062</v>
       </c>
       <c r="G61">
-        <v>-8.405499448696652</v>
+        <v>-5.615606716932184</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.8807353448964557</v>
       </c>
       <c r="E62">
-        <v>-21.56894716475522</v>
+        <v>-15.94629421040353</v>
       </c>
       <c r="F62">
-        <v>6.442165927382288</v>
+        <v>7.209131424816682</v>
       </c>
       <c r="G62">
-        <v>-8.312218207036608</v>
+        <v>-6.212229923474099</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.6552695465493102</v>
       </c>
       <c r="E63">
-        <v>-17.87696834730772</v>
+        <v>-16.57536264870505</v>
       </c>
       <c r="F63">
-        <v>5.7171903735958</v>
+        <v>6.822600284057184</v>
       </c>
       <c r="G63">
-        <v>-8.315144729293324</v>
+        <v>-5.205195075883196</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.4446324617739036</v>
       </c>
       <c r="E64">
-        <v>-18.34443819064552</v>
+        <v>-16.22684676060073</v>
       </c>
       <c r="F64">
-        <v>6.157333452664483</v>
+        <v>6.704877678975734</v>
       </c>
       <c r="G64">
-        <v>-8.244017658382083</v>
+        <v>-5.939033773936822</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.2511299747560908</v>
       </c>
       <c r="E65">
-        <v>-18.55764327540065</v>
+        <v>-16.36150546369282</v>
       </c>
       <c r="F65">
-        <v>6.391128554961004</v>
+        <v>7.235766750286298</v>
       </c>
       <c r="G65">
-        <v>-8.085935798336344</v>
+        <v>-5.643839049291089</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.07606413788637768</v>
       </c>
       <c r="E66">
-        <v>-19.61365171467132</v>
+        <v>-17.45159066987121</v>
       </c>
       <c r="F66">
-        <v>5.872674935101267</v>
+        <v>6.892620523881019</v>
       </c>
       <c r="G66">
-        <v>-8.436813898952618</v>
+        <v>-5.684393232147161</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.07681220417347945</v>
       </c>
       <c r="E67">
-        <v>-19.69861947247724</v>
+        <v>-15.56334833441889</v>
       </c>
       <c r="F67">
-        <v>5.600902500856</v>
+        <v>6.673837095658032</v>
       </c>
       <c r="G67">
-        <v>-7.406446326400933</v>
+        <v>-5.208671148699431</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.2053480782689906</v>
       </c>
       <c r="E68">
-        <v>-19.42685669032893</v>
+        <v>-16.43116245087881</v>
       </c>
       <c r="F68">
-        <v>5.795401510298518</v>
+        <v>6.691757996050196</v>
       </c>
       <c r="G68">
-        <v>-7.391406518016024</v>
+        <v>-5.86831721067245</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.3079639634079077</v>
       </c>
       <c r="E69">
-        <v>-18.22944665016875</v>
+        <v>-15.32501927586921</v>
       </c>
       <c r="F69">
-        <v>5.718374938981803</v>
+        <v>6.701534388138035</v>
       </c>
       <c r="G69">
-        <v>-8.611683535428002</v>
+        <v>-5.401325035811778</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.3833170781621077</v>
       </c>
       <c r="E70">
-        <v>-19.40550946385677</v>
+        <v>-15.44672201482535</v>
       </c>
       <c r="F70">
-        <v>5.261409374697067</v>
+        <v>6.763000906160564</v>
       </c>
       <c r="G70">
-        <v>-7.986880965255811</v>
+        <v>-4.766815946118445</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.4306114629819128</v>
       </c>
       <c r="E71">
-        <v>-18.83237220802399</v>
+        <v>-15.68163660397325</v>
       </c>
       <c r="F71">
-        <v>5.749582852514871</v>
+        <v>6.711057299800618</v>
       </c>
       <c r="G71">
-        <v>-8.417692187917789</v>
+        <v>-6.230411439575776</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.4488371911443841</v>
       </c>
       <c r="E72">
-        <v>-18.74169404449439</v>
+        <v>-16.53103341664396</v>
       </c>
       <c r="F72">
-        <v>6.17169237322461</v>
+        <v>6.095921606890539</v>
       </c>
       <c r="G72">
-        <v>-8.287511605677027</v>
+        <v>-5.503256732965938</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.4377356280568028</v>
       </c>
       <c r="E73">
-        <v>-19.27426070169246</v>
+        <v>-16.29775813508684</v>
       </c>
       <c r="F73">
-        <v>5.524527026317885</v>
+        <v>6.311263996922299</v>
       </c>
       <c r="G73">
-        <v>-7.006055706699319</v>
+        <v>-6.042647228224932</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.3968398487070682</v>
       </c>
       <c r="E74">
-        <v>-17.2506758635729</v>
+        <v>-15.81878143929555</v>
       </c>
       <c r="F74">
-        <v>5.488335654489575</v>
+        <v>6.36110852028355</v>
       </c>
       <c r="G74">
-        <v>-7.071389322916835</v>
+        <v>-6.531134775272092</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.3260846255736881</v>
       </c>
       <c r="E75">
-        <v>-20.6671830786598</v>
+        <v>-15.61408988567484</v>
       </c>
       <c r="F75">
-        <v>5.65281794272425</v>
+        <v>5.878634210197006</v>
       </c>
       <c r="G75">
-        <v>-7.964395739953082</v>
+        <v>-5.647914330849932</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.225779526492786</v>
       </c>
       <c r="E76">
-        <v>-18.89391416978823</v>
+        <v>-17.44383339389607</v>
       </c>
       <c r="F76">
-        <v>5.155025462625138</v>
+        <v>5.855913749073022</v>
       </c>
       <c r="G76">
-        <v>-7.445242609575653</v>
+        <v>-5.02802461025802</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.09670022691181096</v>
       </c>
       <c r="E77">
-        <v>-20.01661344576986</v>
+        <v>-16.46111830643954</v>
       </c>
       <c r="F77">
-        <v>5.477243814966089</v>
+        <v>5.605163622776</v>
       </c>
       <c r="G77">
-        <v>-6.926973394857209</v>
+        <v>-5.927503143823541</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.05840315596224218</v>
       </c>
       <c r="E78">
-        <v>-21.24455445768976</v>
+        <v>-17.16000675699133</v>
       </c>
       <c r="F78">
-        <v>5.383646582123773</v>
+        <v>6.010099430490899</v>
       </c>
       <c r="G78">
-        <v>-6.813173391944762</v>
+        <v>-5.693702486203592</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.2381756901046277</v>
       </c>
       <c r="E79">
-        <v>-20.83653894959866</v>
+        <v>-16.08529572006897</v>
       </c>
       <c r="F79">
-        <v>5.170371797129401</v>
+        <v>5.574767509297675</v>
       </c>
       <c r="G79">
-        <v>-6.179587944456885</v>
+        <v>-3.79944805517909</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.4406672182561103</v>
       </c>
       <c r="E80">
-        <v>-21.28934106562562</v>
+        <v>-18.50959616617927</v>
       </c>
       <c r="F80">
-        <v>5.393282151753137</v>
+        <v>6.060860128199647</v>
       </c>
       <c r="G80">
-        <v>-6.789145452420732</v>
+        <v>-3.779283522299389</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.663764320986211</v>
       </c>
       <c r="E81">
-        <v>-22.60998899743054</v>
+        <v>-17.98873561429103</v>
       </c>
       <c r="F81">
-        <v>5.534245432687529</v>
+        <v>5.962460021155899</v>
       </c>
       <c r="G81">
-        <v>-7.246907826317916</v>
+        <v>-4.359281169143083</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.9055346518663202</v>
       </c>
       <c r="E82">
-        <v>-23.39734118772216</v>
+        <v>-19.69150071133718</v>
       </c>
       <c r="F82">
-        <v>5.092841578431784</v>
+        <v>5.855877300907299</v>
       </c>
       <c r="G82">
-        <v>-5.734382469790156</v>
+        <v>-5.042279819350122</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.162110502023753</v>
       </c>
       <c r="E83">
-        <v>-22.69016110126233</v>
+        <v>-19.79972218317249</v>
       </c>
       <c r="F83">
-        <v>5.634182989630872</v>
+        <v>5.671946602789697</v>
       </c>
       <c r="G83">
-        <v>-5.863510298549429</v>
+        <v>-3.555493954390196</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.431085246000143</v>
       </c>
       <c r="E84">
-        <v>-24.41209070030895</v>
+        <v>-22.55050749133979</v>
       </c>
       <c r="F84">
-        <v>5.682090790004379</v>
+        <v>5.712558143079345</v>
       </c>
       <c r="G84">
-        <v>-5.731214277709074</v>
+        <v>-4.217718931338308</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.711492895011359</v>
       </c>
       <c r="E85">
-        <v>-24.67890386036688</v>
+        <v>-22.74419485312186</v>
       </c>
       <c r="F85">
-        <v>5.207504194327292</v>
+        <v>5.841771860772429</v>
       </c>
       <c r="G85">
-        <v>-5.289726545682947</v>
+        <v>-3.973771451640493</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.001921894346533</v>
       </c>
       <c r="E86">
-        <v>-26.59074407387317</v>
+        <v>-23.26224322265133</v>
       </c>
       <c r="F86">
-        <v>5.541599678489583</v>
+        <v>6.112485641476918</v>
       </c>
       <c r="G86">
-        <v>-5.884075407439381</v>
+        <v>-3.768861924941763</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.301004572670546</v>
       </c>
       <c r="E87">
-        <v>-27.95775452256862</v>
+        <v>-23.65596233830021</v>
       </c>
       <c r="F87">
-        <v>5.812356534299018</v>
+        <v>5.858272939436195</v>
       </c>
       <c r="G87">
-        <v>-5.864897417130384</v>
+        <v>-3.065205470569673</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.606121329098674</v>
       </c>
       <c r="E88">
-        <v>-28.30416467025937</v>
+        <v>-25.41656057689833</v>
       </c>
       <c r="F88">
-        <v>5.2741132171864</v>
+        <v>6.104539941349265</v>
       </c>
       <c r="G88">
-        <v>-5.98755643990592</v>
+        <v>-4.166392233297447</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.91340807745041</v>
       </c>
       <c r="E89">
-        <v>-30.44953375986721</v>
+        <v>-27.52144058040358</v>
       </c>
       <c r="F89">
-        <v>5.419640802510218</v>
+        <v>5.692365859268704</v>
       </c>
       <c r="G89">
-        <v>-5.354272252062117</v>
+        <v>-3.393346744422232</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.221980805938708</v>
       </c>
       <c r="E90">
-        <v>-31.67999260333537</v>
+        <v>-28.17744438210273</v>
       </c>
       <c r="F90">
-        <v>5.391868956963961</v>
+        <v>5.622358873323313</v>
       </c>
       <c r="G90">
-        <v>-5.846626516299146</v>
+        <v>-2.524864848740908</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.528781632157962</v>
       </c>
       <c r="E91">
-        <v>-33.62112525096027</v>
+        <v>-30.29126359329913</v>
       </c>
       <c r="F91">
-        <v>5.29578165170883</v>
+        <v>5.747889669543549</v>
       </c>
       <c r="G91">
-        <v>-4.018533337876979</v>
+        <v>-2.634367763543381</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.829741435733078</v>
       </c>
       <c r="E92">
-        <v>-34.37010994522191</v>
+        <v>-31.47041935473439</v>
       </c>
       <c r="F92">
-        <v>5.04690529247694</v>
+        <v>5.711902076096328</v>
       </c>
       <c r="G92">
-        <v>-5.765147369486603</v>
+        <v>-3.034592855968032</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.12010315496669</v>
       </c>
       <c r="E93">
-        <v>-35.78936087006984</v>
+        <v>-33.15195270139558</v>
       </c>
       <c r="F93">
-        <v>5.290294546032686</v>
+        <v>5.196674118903092</v>
       </c>
       <c r="G93">
-        <v>-4.92305052175327</v>
+        <v>-2.348750447142759</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.391513481770674</v>
       </c>
       <c r="E94">
-        <v>-37.74754548657062</v>
+        <v>-35.31317824274128</v>
       </c>
       <c r="F94">
-        <v>5.211892884827324</v>
+        <v>5.398928303970618</v>
       </c>
       <c r="G94">
-        <v>-4.875285970712666</v>
+        <v>-2.577489280633163</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.641198100989737</v>
       </c>
       <c r="E95">
-        <v>-38.65109605566207</v>
+        <v>-37.20130963058041</v>
       </c>
       <c r="F95">
-        <v>5.148125162159817</v>
+        <v>5.30440992657639</v>
       </c>
       <c r="G95">
-        <v>-4.961807078381518</v>
+        <v>-3.04268713981155</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.863359338614455</v>
       </c>
       <c r="E96">
-        <v>-41.83356946979556</v>
+        <v>-39.27425709962058</v>
       </c>
       <c r="F96">
-        <v>4.890087059452966</v>
+        <v>4.99189175652222</v>
       </c>
       <c r="G96">
-        <v>-4.177939416138425</v>
+        <v>-2.86871466117731</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.054574462043915</v>
       </c>
       <c r="E97">
-        <v>-42.6415964081692</v>
+        <v>-41.61656499534799</v>
       </c>
       <c r="F97">
-        <v>5.487868455274396</v>
+        <v>5.567141558987503</v>
       </c>
       <c r="G97">
-        <v>-5.026197189120342</v>
+        <v>-2.400083766274698</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.207329967779113</v>
       </c>
       <c r="E98">
-        <v>-46.47339412484052</v>
+        <v>-42.96009077783967</v>
       </c>
       <c r="F98">
-        <v>4.646505624659771</v>
+        <v>5.082806735714271</v>
       </c>
       <c r="G98">
-        <v>-6.026730125272116</v>
+        <v>-2.698575794277545</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.320233727588429</v>
       </c>
       <c r="E99">
-        <v>-46.72947480150027</v>
+        <v>-44.91890485222752</v>
       </c>
       <c r="F99">
-        <v>4.807006779156593</v>
+        <v>4.567370029935529</v>
       </c>
       <c r="G99">
-        <v>-4.391595404151909</v>
+        <v>-1.730446477864158</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>5.385022074302034</v>
       </c>
       <c r="E100">
-        <v>-49.51294889929194</v>
+        <v>-46.3785044804838</v>
       </c>
       <c r="F100">
-        <v>4.776393633418734</v>
+        <v>4.587179608006076</v>
       </c>
       <c r="G100">
-        <v>-5.046590149642252</v>
+        <v>-3.015808820578207</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>5.408880033479999</v>
       </c>
       <c r="E101">
-        <v>-51.84847653731137</v>
+        <v>-49.40963629328095</v>
       </c>
       <c r="F101">
-        <v>4.369052246766105</v>
+        <v>4.050193752610908</v>
       </c>
       <c r="G101">
-        <v>-4.768169959244007</v>
+        <v>-2.156857985504444</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>5.375158153228214</v>
       </c>
       <c r="E102">
-        <v>-52.88429251098184</v>
+        <v>-51.07540262556594</v>
       </c>
       <c r="F102">
-        <v>4.249164289293739</v>
+        <v>4.184225255118673</v>
       </c>
       <c r="G102">
-        <v>-4.910602870525611</v>
+        <v>-2.621231518843553</v>
       </c>
     </row>
   </sheetData>
